--- a/supplementary-materials/tables/Table_S15.xlsx
+++ b/supplementary-materials/tables/Table_S15.xlsx
@@ -217,7 +217,7 @@
     <t>Completed H4 P0 joint posterior from S5-S6</t>
   </si>
   <si>
-    <t>300 matched posterior draws</t>
+    <t/>
   </si>
   <si>
     <t>HEX-week predictions joined to overlay weights</t>
